--- a/dataset/lecture_3_output/MACCS_output.xlsx
+++ b/dataset/lecture_3_output/MACCS_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,847 +429,847 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CAS</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>PubChem_CID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MACCS_1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MACCS_2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MACCS_3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MACCS_4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MACCS_5</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MACCS_6</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MACCS_7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MACCS_8</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MACCS_9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MACCS_10</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MACCS_11</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MACCS_12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MACCS_13</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MACCS_14</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MACCS_15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MACCS_16</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MACCS_17</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MACCS_18</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MACCS_19</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MACCS_20</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MACCS_21</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MACCS_22</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MACCS_23</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MACCS_24</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_25</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_26</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_27</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MACCS_28</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_29</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_30</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_31</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_32</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_33</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_34</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_35</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_36</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_37</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>MACCS_38</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>MACCS_39</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MACCS_40</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_41</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>MACCS_42</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>MACCS_43</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MACCS_44</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MACCS_45</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>MACCS_46</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MACCS_47</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MACCS_48</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MACCS_49</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_50</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_51</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_52</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_53</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACCS_54</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_55</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_56</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_57</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_58</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_59</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_60</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_61</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_62</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_63</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>MACCS_64</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>MACCS_65</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MACCS_66</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_67</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MACCS_68</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MACCS_69</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MACCS_70</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MACCS_71</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>MACCS_72</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>MACCS_73</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>MACCS_74</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>MACCS_75</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_76</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_77</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_78</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_79</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>MACCS_80</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_81</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_82</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_83</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_84</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_85</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_86</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_87</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_88</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_89</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>MACCS_90</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>MACCS_91</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MACCS_92</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_93</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MACCS_94</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MACCS_95</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MACCS_96</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MACCS_97</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MACCS_98</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MACCS_99</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MACCS_100</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MACCS_101</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_102</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_103</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_104</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_105</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACCS_106</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_107</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_108</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_109</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_110</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_111</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_112</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_113</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_114</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_115</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>MACCS_116</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>MACCS_117</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>MACCS_118</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_119</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>MACCS_120</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MACCS_121</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MACCS_122</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MACCS_123</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>MACCS_124</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>MACCS_125</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>MACCS_126</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>MACCS_127</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_128</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_129</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_130</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_131</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>MACCS_132</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_133</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_134</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_135</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_136</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_137</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_138</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_139</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_140</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_141</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>MACCS_142</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>MACCS_143</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>MACCS_144</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_145</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>MACCS_146</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>MACCS_147</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>MACCS_148</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>MACCS_149</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>MACCS_150</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>MACCS_151</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>MACCS_152</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>MACCS_153</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_154</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>MACCS_155</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MACCS_156</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>MACCS_157</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>MACCS_158</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>MACCS_159</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>MACCS_160</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>MACCS_161</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>MACCS_162</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>MACCS_163</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>MACCS_164</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>MACCS_165</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>MACCS_166</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>MACCS_167</t>
         </is>
